--- a/experiment/baseline.xlsx
+++ b/experiment/baseline.xlsx
@@ -4,10 +4,10 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="14925" windowHeight="4440"/>
+    <workbookView windowWidth="25600" windowHeight="12790"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="baseline_modified" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,7 +27,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="563" uniqueCount="298">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="565" uniqueCount="302">
+  <si>
+    <t>APKS</t>
+  </si>
   <si>
     <t>TreeMind</t>
   </si>
@@ -61,7 +64,7 @@
     <t>sdbviewer-10</t>
   </si>
   <si>
-    <t>1.07.826</t>
+    <t>2.47.334</t>
   </si>
   <si>
     <t>1.27.513</t>
@@ -79,7 +82,7 @@
     <t>Anki-Android-9914</t>
   </si>
   <si>
-    <t>14.08.895</t>
+    <t>7.42.208</t>
   </si>
   <si>
     <t>4.18.445</t>
@@ -94,7 +97,7 @@
     <t>Alarmio-47</t>
   </si>
   <si>
-    <t>3.01.553</t>
+    <t>4.53.889</t>
   </si>
   <si>
     <t>1.31.395</t>
@@ -112,7 +115,7 @@
     <t>plusTimer-19</t>
   </si>
   <si>
-    <t>0.17.613</t>
+    <t>0.13.275</t>
   </si>
   <si>
     <t>0.17.419</t>
@@ -136,7 +139,7 @@
     <t>ankidroid-3370</t>
   </si>
   <si>
-    <t>1.44.553</t>
+    <t>2.35.055</t>
   </si>
   <si>
     <t>1.47.823</t>
@@ -157,7 +160,7 @@
     <t>ankidroid-2564</t>
   </si>
   <si>
-    <t>1.03.786</t>
+    <t>2.44.019</t>
   </si>
   <si>
     <t>0.51.749</t>
@@ -166,7 +169,7 @@
     <t>ankidroid-2681</t>
   </si>
   <si>
-    <t>2.47.560</t>
+    <t>2.08.827</t>
   </si>
   <si>
     <t>1.56.427</t>
@@ -175,7 +178,7 @@
     <t>WhereYouGo-368</t>
   </si>
   <si>
-    <t>2.17.437</t>
+    <t>1.57.287</t>
   </si>
   <si>
     <t>1.31.117</t>
@@ -193,7 +196,7 @@
     <t>food-tracker-55</t>
   </si>
   <si>
-    <t>1.07.129</t>
+    <t>7.31.040</t>
   </si>
   <si>
     <t>2.37.106</t>
@@ -208,7 +211,7 @@
     <t>Mesh-495</t>
   </si>
   <si>
-    <t>9.33.528</t>
+    <t>8.43.507</t>
   </si>
   <si>
     <t>5.15.765</t>
@@ -223,13 +226,13 @@
     <t>FakeStandby-30</t>
   </si>
   <si>
-    <t>3.41.243</t>
+    <t>3.41.593</t>
   </si>
   <si>
     <t>revolution-irc-183</t>
   </si>
   <si>
-    <t>23.50.998</t>
+    <t>9.21.976</t>
   </si>
   <si>
     <t>5.21.356</t>
@@ -241,13 +244,13 @@
     <t>ankidroid-3224</t>
   </si>
   <si>
-    <t>0.50.337</t>
+    <t>0.21.583</t>
   </si>
   <si>
     <t>pedometer-101</t>
   </si>
   <si>
-    <t>2.13.038</t>
+    <t>6.04.819</t>
   </si>
   <si>
     <t>0.46.021</t>
@@ -256,7 +259,7 @@
     <t>andror2-7</t>
   </si>
   <si>
-    <t>3.23.755</t>
+    <t>4.05.725</t>
   </si>
   <si>
     <t>0.34.502</t>
@@ -268,7 +271,7 @@
     <t>andror2-11</t>
   </si>
   <si>
-    <t>0.20.269</t>
+    <t>0.52.048</t>
   </si>
   <si>
     <t>0.13.761</t>
@@ -286,7 +289,7 @@
     <t>andror2-23</t>
   </si>
   <si>
-    <t>1.09.100</t>
+    <t>2.29.604</t>
   </si>
   <si>
     <t>0.12.234</t>
@@ -307,7 +310,7 @@
     <t>andror2-162</t>
   </si>
   <si>
-    <t>2.01.675</t>
+    <t>2.33.880</t>
   </si>
   <si>
     <t>0.52.817</t>
@@ -322,7 +325,7 @@
     <t>andror2-198</t>
   </si>
   <si>
-    <t>1.32.610</t>
+    <t>1.09.257</t>
   </si>
   <si>
     <t>andror2-276</t>
@@ -331,7 +334,7 @@
     <t>recdroid-1</t>
   </si>
   <si>
-    <t>3.14.786</t>
+    <t>5.04.542</t>
   </si>
   <si>
     <t>0.45.041</t>
@@ -349,7 +352,7 @@
     <t>recdroid-2</t>
   </si>
   <si>
-    <t>4.17.318</t>
+    <t>6.11.305</t>
   </si>
   <si>
     <t>2.31.865</t>
@@ -364,7 +367,7 @@
     <t>recdroid-3</t>
   </si>
   <si>
-    <t>2.06.807</t>
+    <t>3.21.190</t>
   </si>
   <si>
     <t>0.40.967</t>
@@ -385,7 +388,7 @@
     <t>recdroid-7</t>
   </si>
   <si>
-    <t>3.18.585</t>
+    <t>1.47.461</t>
   </si>
   <si>
     <t>0.27.403</t>
@@ -406,7 +409,7 @@
     <t>recdroid-9</t>
   </si>
   <si>
-    <t>3.41.129</t>
+    <t>5.05.162</t>
   </si>
   <si>
     <t>2.20.189</t>
@@ -424,13 +427,13 @@
     <t>recdroid-11</t>
   </si>
   <si>
-    <t>1.34.988</t>
+    <t>1.16.092</t>
   </si>
   <si>
     <t>recdroid-12</t>
   </si>
   <si>
-    <t>1.55.505</t>
+    <t>10.20.261</t>
   </si>
   <si>
     <t>0.25.406</t>
@@ -445,10 +448,13 @@
     <t>20.16.502</t>
   </si>
   <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
     <t>recdroid-13</t>
   </si>
   <si>
-    <t>2.34.317</t>
+    <t>2.09.522</t>
   </si>
   <si>
     <t>0.33.679</t>
@@ -466,7 +472,7 @@
     <t>recdroid-14</t>
   </si>
   <si>
-    <t>3.33.467</t>
+    <t>2.18.212</t>
   </si>
   <si>
     <t>1.36.740</t>
@@ -484,7 +490,7 @@
     <t>recdroid-15</t>
   </si>
   <si>
-    <t>5.44.074</t>
+    <t>3.07.228</t>
   </si>
   <si>
     <t>0.40.742</t>
@@ -493,13 +499,13 @@
     <t>recdroid-17</t>
   </si>
   <si>
-    <t>1.07.909</t>
+    <t>1.23.523</t>
   </si>
   <si>
     <t>recdroid-21</t>
   </si>
   <si>
-    <t>3.24.857</t>
+    <t>1.27.685</t>
   </si>
   <si>
     <t>0.48.693</t>
@@ -514,7 +520,7 @@
     <t>recdroid-24</t>
   </si>
   <si>
-    <t>4.39.605</t>
+    <t>7.36.551</t>
   </si>
   <si>
     <t>0.23.204</t>
@@ -529,7 +535,7 @@
     <t>recdroid-26</t>
   </si>
   <si>
-    <t>1.41.996</t>
+    <t>2.02.047</t>
   </si>
   <si>
     <t>0.23.622</t>
@@ -547,7 +553,7 @@
     <t>recdroid-27</t>
   </si>
   <si>
-    <t>3.34.568</t>
+    <t>2.09.827</t>
   </si>
   <si>
     <t>0.59.017</t>
@@ -562,19 +568,19 @@
     <t>recdroid-28</t>
   </si>
   <si>
-    <t>17.28.345</t>
+    <t>9.17.985</t>
   </si>
   <si>
     <t>recdroid-29</t>
   </si>
   <si>
-    <t>2.57.714</t>
+    <t>2.49.731</t>
   </si>
   <si>
     <t>recdroid-30</t>
   </si>
   <si>
-    <t>2.13.791</t>
+    <t>2.30.697</t>
   </si>
   <si>
     <t>1.26.898</t>
@@ -592,7 +598,7 @@
     <t>recdroid-31</t>
   </si>
   <si>
-    <t>2.54.398</t>
+    <t>0.41.178</t>
   </si>
   <si>
     <t>1.51.438</t>
@@ -610,6 +616,9 @@
     <t>recdroid-33</t>
   </si>
   <si>
+    <t>8.02.324</t>
+  </si>
+  <si>
     <t>recdroid-34</t>
   </si>
   <si>
@@ -619,7 +628,7 @@
     <t>recdroid-38</t>
   </si>
   <si>
-    <t>0.13.680</t>
+    <t>0.15.477</t>
   </si>
   <si>
     <t>0.16.188</t>
@@ -640,9 +649,6 @@
     <t>recdroid-42</t>
   </si>
   <si>
-    <t>9.13.038</t>
-  </si>
-  <si>
     <t>1.17.487</t>
   </si>
   <si>
@@ -658,7 +664,7 @@
     <t>recdroid-53</t>
   </si>
   <si>
-    <t>6.27.823</t>
+    <t>6.46.094</t>
   </si>
   <si>
     <t>2.46.543</t>
@@ -679,13 +685,13 @@
     <t>recdroid-56</t>
   </si>
   <si>
-    <t>2.17.731</t>
+    <t>12.23.918</t>
   </si>
   <si>
     <t>recdroid-57</t>
   </si>
   <si>
-    <t>3.52.746</t>
+    <t>7.29.103</t>
   </si>
   <si>
     <t>3.13.314</t>
@@ -694,7 +700,7 @@
     <t>recdroid-58</t>
   </si>
   <si>
-    <t>1.15.350</t>
+    <t>1.28.741</t>
   </si>
   <si>
     <t>0.24.272</t>
@@ -712,7 +718,7 @@
     <t>recdroid-60</t>
   </si>
   <si>
-    <t>15.30.221</t>
+    <t>5.11.501</t>
   </si>
   <si>
     <t>0.48.078</t>
@@ -721,7 +727,7 @@
     <t>recdroid-61</t>
   </si>
   <si>
-    <t>4.07.122</t>
+    <t>3.58.856</t>
   </si>
   <si>
     <t>2.29.056</t>
@@ -733,16 +739,13 @@
     <t>recdroid-62</t>
   </si>
   <si>
-    <t>7.06.762</t>
-  </si>
-  <si>
     <t>2.18.530</t>
   </si>
   <si>
     <t>recdroid-64</t>
   </si>
   <si>
-    <t>2.13.452</t>
+    <t>1.33.617</t>
   </si>
   <si>
     <t>1.17.513</t>
@@ -760,7 +763,7 @@
     <t>saner2022-2</t>
   </si>
   <si>
-    <t>4.13.849</t>
+    <t>2.55.774</t>
   </si>
   <si>
     <t>0.38.074</t>
@@ -775,7 +778,7 @@
     <t>saner2022-11</t>
   </si>
   <si>
-    <t>0.21.559</t>
+    <t>0.14.072</t>
   </si>
   <si>
     <t>0.13.025</t>
@@ -796,6 +799,9 @@
     <t>saner2022-23</t>
   </si>
   <si>
+    <t>5.19.409</t>
+  </si>
+  <si>
     <t>1.58.626</t>
   </si>
   <si>
@@ -814,7 +820,7 @@
     <t>saner2022-1089</t>
   </si>
   <si>
-    <t>3.16.219</t>
+    <t>3.34.890</t>
   </si>
   <si>
     <t>0.53.337</t>
@@ -835,24 +841,27 @@
     <t>saner2022-1133</t>
   </si>
   <si>
+    <t>2.19.893</t>
+  </si>
+  <si>
+    <t>0.52.137</t>
+  </si>
+  <si>
+    <t>1.22.064</t>
+  </si>
+  <si>
     <t>2.47.914</t>
   </si>
   <si>
-    <t>0.52.137</t>
-  </si>
-  <si>
-    <t>1.22.064</t>
-  </si>
-  <si>
     <t>saner2022-1160</t>
   </si>
   <si>
+    <t>10.01.028</t>
+  </si>
+  <si>
     <t>saner2022-1207</t>
   </si>
   <si>
-    <t>10.12.302</t>
-  </si>
-  <si>
     <t>1.24.699</t>
   </si>
   <si>
@@ -865,25 +874,28 @@
     <t>saner2022-1215</t>
   </si>
   <si>
-    <t>1.28.669</t>
+    <t>1.55.607</t>
   </si>
   <si>
     <t>saner2022-1227</t>
   </si>
   <si>
-    <t>17.33.244</t>
+    <t>11.15.521</t>
   </si>
   <si>
     <t>saner2022-1299</t>
   </si>
   <si>
+    <t>5.13.502</t>
+  </si>
+  <si>
     <t>6.32.565</t>
   </si>
   <si>
     <t>saner2022-1430</t>
   </si>
   <si>
-    <t>3.22.292</t>
+    <t>1.26.575</t>
   </si>
   <si>
     <t>2.34.577</t>
@@ -904,7 +916,7 @@
     <t>saner2022-1645</t>
   </si>
   <si>
-    <t>6.24.785</t>
+    <t>3.12.773</t>
   </si>
   <si>
     <t>9.45.421</t>
@@ -919,13 +931,13 @@
     <t>yakusu-35</t>
   </si>
   <si>
-    <t>2.18.938</t>
+    <t>1.49.408</t>
   </si>
   <si>
     <t>yakusu-98</t>
   </si>
   <si>
-    <t>11.11.319</t>
+    <t>2.17.617</t>
   </si>
   <si>
     <t>21.18.271</t>
@@ -1300,27 +1312,12 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="9">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1423,7 +1420,9 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -1445,7 +1444,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1457,34 +1456,34 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1569,11 +1568,12 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1627,7 +1627,221 @@
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <dxfs count="17">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="double">
+          <color theme="4"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <left style="thin">
+          <color theme="4"/>
+        </left>
+        <right style="thin">
+          <color theme="4"/>
+        </right>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+        <horizontal style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+  </dxfs>
+  <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
+      <tableStyleElement type="wholeTable" dxfId="6"/>
+      <tableStyleElement type="headerRow" dxfId="5"/>
+      <tableStyleElement type="totalRow" dxfId="4"/>
+      <tableStyleElement type="firstColumn" dxfId="3"/>
+      <tableStyleElement type="lastColumn" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
+    </tableStyle>
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
+      <tableStyleElement type="headerRow" dxfId="16"/>
+      <tableStyleElement type="totalRow" dxfId="15"/>
+      <tableStyleElement type="firstRowStripe" dxfId="14"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
+      <tableStyleElement type="pageFieldValues" dxfId="7"/>
+    </tableStyle>
+  </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1637,7 +1851,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -1647,39 +1861,39 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="800080"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1711,6 +1925,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -1745,6 +1960,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -1756,160 +1972,131 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="35000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="80000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
+                <a:alpha val="63000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="40000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
@@ -1921,1897 +2108,1903 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F94"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="5"/>
+  <dimension ref="A1:J94"/>
+  <sheetFormatPr defaultColWidth="9.81818181818182" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="32.9083333333333" style="1" customWidth="1"/>
-    <col min="2" max="2" width="18.3666666666667" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15.0916666666667" style="1" customWidth="1"/>
-    <col min="4" max="4" width="16.3666666666667" style="1" customWidth="1"/>
-    <col min="5" max="5" width="16.1833333333333" style="1" customWidth="1"/>
-    <col min="6" max="6" width="15.1833333333333" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="9" style="1"/>
+    <col min="1" max="1" width="21.6363636363636" style="1" customWidth="1"/>
+    <col min="2" max="2" width="15.9090909090909" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.6363636363636" style="1" customWidth="1"/>
+    <col min="4" max="4" width="13.5454545454545" style="1" customWidth="1"/>
+    <col min="5" max="5" width="11.9090909090909" style="1" customWidth="1"/>
+    <col min="6" max="6" width="12" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="9.81818181818182" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6">
-      <c r="B1" s="2" t="s">
+    <row r="1" spans="1:6">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="2" t="s">
-        <v>5</v>
+      <c r="A2" s="1" t="s">
+        <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="2" t="s">
-        <v>7</v>
+      <c r="A3" s="1" t="s">
+        <v>8</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="2" t="s">
-        <v>13</v>
+      <c r="A4" s="1" t="s">
+        <v>14</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
-        <v>17</v>
+      <c r="A5" s="1" t="s">
+        <v>18</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="2" t="s">
-        <v>18</v>
+      <c r="A6" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="2" t="s">
-        <v>24</v>
+      <c r="A7" s="1" t="s">
+        <v>25</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="2" t="s">
-        <v>30</v>
+      <c r="A8" s="1" t="s">
+        <v>31</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="2" t="s">
-        <v>31</v>
+      <c r="A9" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="2" t="s">
-        <v>32</v>
+      <c r="A10" s="1" t="s">
+        <v>33</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="2" t="s">
-        <v>38</v>
+      <c r="A11" s="1" t="s">
+        <v>39</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="2" t="s">
-        <v>39</v>
+      <c r="A12" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="2" t="s">
-        <v>42</v>
+      <c r="A13" s="1" t="s">
+        <v>43</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="2" t="s">
-        <v>45</v>
+      <c r="A14" s="1" t="s">
+        <v>46</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="2" t="s">
-        <v>51</v>
+      <c r="A15" s="1" t="s">
+        <v>52</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="2" t="s">
-        <v>54</v>
+      <c r="A16" s="1" t="s">
+        <v>55</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17" spans="1:6">
-      <c r="A17" s="2" t="s">
-        <v>55</v>
+      <c r="A17" s="1" t="s">
+        <v>56</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18" spans="1:6">
-      <c r="A18" s="2" t="s">
-        <v>56</v>
+      <c r="A18" s="1" t="s">
+        <v>57</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="19" spans="1:6">
-      <c r="A19" s="2" t="s">
-        <v>60</v>
+      <c r="A19" s="1" t="s">
+        <v>61</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20" spans="1:6">
-      <c r="A20" s="2" t="s">
-        <v>61</v>
+      <c r="A20" s="1" t="s">
+        <v>62</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21" spans="1:6">
-      <c r="A21" s="2" t="s">
-        <v>63</v>
+      <c r="A21" s="1" t="s">
+        <v>64</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:6">
-      <c r="A22" s="2" t="s">
-        <v>67</v>
+      <c r="A22" s="1" t="s">
+        <v>68</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23" spans="1:6">
-      <c r="A23" s="2" t="s">
-        <v>69</v>
+      <c r="A23" s="1" t="s">
+        <v>70</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24" spans="1:6">
-      <c r="A24" s="2" t="s">
-        <v>72</v>
+      <c r="A24" s="1" t="s">
+        <v>73</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25" spans="1:6">
-      <c r="A25" s="2" t="s">
-        <v>76</v>
+      <c r="A25" s="1" t="s">
+        <v>77</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="26" spans="1:6">
-      <c r="A26" s="2" t="s">
-        <v>82</v>
+      <c r="A26" s="1" t="s">
+        <v>83</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="27" spans="1:6">
-      <c r="A27" s="2" t="s">
-        <v>88</v>
+      <c r="A27" s="1" t="s">
+        <v>89</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28" spans="1:6">
-      <c r="A28" s="2" t="s">
-        <v>89</v>
+      <c r="A28" s="1" t="s">
+        <v>90</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29" spans="1:6">
-      <c r="A29" s="2" t="s">
-        <v>92</v>
+      <c r="A29" s="1" t="s">
+        <v>93</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30" spans="1:6">
-      <c r="A30" s="2" t="s">
-        <v>93</v>
+      <c r="A30" s="1" t="s">
+        <v>94</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31" spans="1:6">
-      <c r="A31" s="2" t="s">
-        <v>94</v>
+      <c r="A31" s="1" t="s">
+        <v>95</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="32" spans="1:6">
-      <c r="A32" s="2" t="s">
-        <v>96</v>
+      <c r="A32" s="1" t="s">
+        <v>97</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33" s="2" t="s">
-        <v>97</v>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10">
+      <c r="A33" s="1" t="s">
+        <v>98</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34" s="2" t="s">
         <v>103</v>
       </c>
+    </row>
+    <row r="34" spans="1:10">
+      <c r="A34" s="1" t="s">
+        <v>104</v>
+      </c>
       <c r="B34" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35" s="2" t="s">
         <v>108</v>
       </c>
+    </row>
+    <row r="35" spans="1:10">
+      <c r="A35" s="1" t="s">
+        <v>109</v>
+      </c>
       <c r="B35" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36" s="2" t="s">
         <v>114</v>
       </c>
+    </row>
+    <row r="36" spans="1:10">
+      <c r="A36" s="1" t="s">
+        <v>115</v>
+      </c>
       <c r="B36" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="A37" s="2" t="s">
-        <v>115</v>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10">
+      <c r="A37" s="1" t="s">
+        <v>116</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38" s="2" t="s">
         <v>121</v>
       </c>
+    </row>
+    <row r="38" spans="1:10">
+      <c r="A38" s="1" t="s">
+        <v>122</v>
+      </c>
       <c r="B38" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39" s="2" t="s">
-        <v>122</v>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10">
+      <c r="A39" s="1" t="s">
+        <v>123</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="A40" s="2" t="s">
         <v>128</v>
       </c>
+    </row>
+    <row r="40" spans="1:10">
+      <c r="A40" s="1" t="s">
+        <v>129</v>
+      </c>
       <c r="B40" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
-      <c r="A41" s="2" t="s">
-        <v>130</v>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10">
+      <c r="A41" s="1" t="s">
+        <v>131</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
-      <c r="A42" s="2" t="s">
         <v>136</v>
       </c>
+      <c r="J41" s="1" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10">
+      <c r="A42" s="1" t="s">
+        <v>138</v>
+      </c>
       <c r="B42" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
-      <c r="A43" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10">
+      <c r="A43" s="1" t="s">
+        <v>144</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
-      <c r="A44" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10">
+      <c r="A44" s="1" t="s">
+        <v>150</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
-      <c r="A45" s="2" t="s">
-        <v>151</v>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10">
+      <c r="A45" s="1" t="s">
+        <v>153</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6">
-      <c r="A46" s="2" t="s">
-        <v>153</v>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10">
+      <c r="A46" s="1" t="s">
+        <v>155</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6">
-      <c r="A47" s="2" t="s">
-        <v>157</v>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10">
+      <c r="A47" s="1" t="s">
+        <v>159</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6">
-      <c r="A48" s="2" t="s">
-        <v>158</v>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10">
+      <c r="A48" s="1" t="s">
+        <v>160</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="49" spans="1:6">
-      <c r="A49" s="2" t="s">
-        <v>162</v>
+      <c r="A49" s="1" t="s">
+        <v>164</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="50" spans="1:6">
-      <c r="A50" s="2" t="s">
-        <v>163</v>
+      <c r="A50" s="1" t="s">
+        <v>165</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="51" spans="1:6">
-      <c r="A51" s="2" t="s">
-        <v>169</v>
+      <c r="A51" s="1" t="s">
+        <v>171</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="52" spans="1:6">
-      <c r="A52" s="2" t="s">
-        <v>174</v>
+      <c r="A52" s="1" t="s">
+        <v>176</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="53" spans="1:6">
-      <c r="A53" s="2" t="s">
-        <v>176</v>
+      <c r="A53" s="1" t="s">
+        <v>178</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="54" spans="1:6">
-      <c r="A54" s="2" t="s">
-        <v>178</v>
+      <c r="A54" s="1" t="s">
+        <v>180</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="55" spans="1:6">
-      <c r="A55" s="2" t="s">
-        <v>184</v>
+      <c r="A55" s="1" t="s">
+        <v>186</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="56" spans="1:6">
-      <c r="A56" s="2" t="s">
-        <v>190</v>
+      <c r="A56" s="1" t="s">
+        <v>192</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>6</v>
+        <v>193</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="57" spans="1:6">
-      <c r="A57" s="2" t="s">
-        <v>191</v>
+      <c r="A57" s="1" t="s">
+        <v>194</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="58" spans="1:6">
-      <c r="A58" s="2" t="s">
-        <v>192</v>
+      <c r="A58" s="1" t="s">
+        <v>195</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="59" spans="1:6">
-      <c r="A59" s="2" t="s">
-        <v>193</v>
+      <c r="A59" s="1" t="s">
+        <v>196</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
     </row>
     <row r="60" spans="1:6">
-      <c r="A60" s="2" t="s">
-        <v>199</v>
+      <c r="A60" s="1" t="s">
+        <v>202</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="61" spans="1:6">
-      <c r="A61" s="2" t="s">
-        <v>200</v>
+      <c r="A61" s="1" t="s">
+        <v>203</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>201</v>
+        <v>7</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="62" spans="1:6">
-      <c r="A62" s="2" t="s">
-        <v>204</v>
+      <c r="A62" s="1" t="s">
+        <v>206</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="63" spans="1:6">
-      <c r="A63" s="2" t="s">
-        <v>205</v>
+      <c r="A63" s="1" t="s">
+        <v>207</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="64" spans="1:6">
-      <c r="A64" s="2" t="s">
-        <v>206</v>
+      <c r="A64" s="1" t="s">
+        <v>208</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="65" spans="1:6">
-      <c r="A65" s="2" t="s">
-        <v>212</v>
+      <c r="A65" s="1" t="s">
+        <v>214</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="66" spans="1:6">
-      <c r="A66" s="2" t="s">
-        <v>213</v>
+      <c r="A66" s="1" t="s">
+        <v>215</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="67" spans="1:6">
-      <c r="A67" s="2" t="s">
-        <v>215</v>
+      <c r="A67" s="1" t="s">
+        <v>217</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="68" spans="1:6">
-      <c r="A68" s="2" t="s">
-        <v>218</v>
+      <c r="A68" s="1" t="s">
+        <v>220</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="69" spans="1:6">
-      <c r="A69" s="2" t="s">
-        <v>224</v>
+      <c r="A69" s="1" t="s">
+        <v>226</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="70" spans="1:6">
-      <c r="A70" s="2" t="s">
-        <v>227</v>
+      <c r="A70" s="1" t="s">
+        <v>229</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="71" spans="1:6">
-      <c r="A71" s="2" t="s">
-        <v>231</v>
+      <c r="A71" s="1" t="s">
+        <v>233</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>232</v>
+        <v>7</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="72" spans="1:6">
-      <c r="A72" s="2" t="s">
-        <v>234</v>
+      <c r="A72" s="1" t="s">
+        <v>235</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="73" spans="1:6">
-      <c r="A73" s="2" t="s">
-        <v>240</v>
+      <c r="A73" s="1" t="s">
+        <v>241</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="74" spans="1:6">
-      <c r="A74" s="2" t="s">
-        <v>244</v>
+      <c r="A74" s="1" t="s">
+        <v>245</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="75" spans="1:6">
-      <c r="A75" s="2" t="s">
-        <v>245</v>
+      <c r="A75" s="1" t="s">
+        <v>246</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="76" spans="1:6">
-      <c r="A76" s="2" t="s">
-        <v>251</v>
+      <c r="A76" s="1" t="s">
+        <v>252</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="A77" s="2" t="s">
-        <v>252</v>
+      <c r="A77" s="1" t="s">
+        <v>253</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>6</v>
+        <v>254</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="78" spans="1:6">
-      <c r="A78" s="2" t="s">
-        <v>254</v>
+      <c r="A78" s="1" t="s">
+        <v>256</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="79" spans="1:6">
-      <c r="A79" s="2" t="s">
-        <v>256</v>
+      <c r="A79" s="1" t="s">
+        <v>258</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="80" spans="1:6">
-      <c r="A80" s="2" t="s">
-        <v>258</v>
+      <c r="A80" s="1" t="s">
+        <v>260</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="81" spans="1:6">
-      <c r="A81" s="2" t="s">
-        <v>264</v>
+      <c r="A81" s="1" t="s">
+        <v>266</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="82" spans="1:6">
-      <c r="A82" s="2" t="s">
-        <v>265</v>
+      <c r="A82" s="1" t="s">
+        <v>267</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
     </row>
     <row r="83" spans="1:6">
-      <c r="A83" s="2" t="s">
-        <v>269</v>
+      <c r="A83" s="1" t="s">
+        <v>272</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>6</v>
+        <v>273</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="84" spans="1:6">
-      <c r="A84" s="2" t="s">
-        <v>270</v>
+      <c r="A84" s="1" t="s">
+        <v>274</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>271</v>
+        <v>7</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="85" spans="1:6">
-      <c r="A85" s="2" t="s">
-        <v>275</v>
+      <c r="A85" s="1" t="s">
+        <v>278</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="86" spans="1:6">
-      <c r="A86" s="2" t="s">
-        <v>277</v>
+      <c r="A86" s="1" t="s">
+        <v>280</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="87" spans="1:6">
-      <c r="A87" s="2" t="s">
-        <v>279</v>
+      <c r="A87" s="1" t="s">
+        <v>282</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>6</v>
+        <v>283</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="88" spans="1:6">
-      <c r="A88" s="2" t="s">
-        <v>281</v>
+      <c r="A88" s="1" t="s">
+        <v>285</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="89" spans="1:6">
-      <c r="A89" s="2" t="s">
-        <v>286</v>
+      <c r="A89" s="1" t="s">
+        <v>290</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="90" spans="1:6">
-      <c r="A90" s="2" t="s">
-        <v>287</v>
+      <c r="A90" s="1" t="s">
+        <v>291</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="91" spans="1:6">
-      <c r="A91" s="2" t="s">
-        <v>288</v>
+      <c r="A91" s="1" t="s">
+        <v>292</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="92" spans="1:6">
-      <c r="A92" s="2" t="s">
-        <v>291</v>
+      <c r="A92" s="1" t="s">
+        <v>295</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="93" spans="1:6">
-      <c r="A93" s="2" t="s">
-        <v>293</v>
+      <c r="A93" s="1" t="s">
+        <v>297</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="94" spans="1:6">
-      <c r="A94" s="2" t="s">
-        <v>295</v>
+      <c r="A94" s="1" t="s">
+        <v>299</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
 </file>
--- a/experiment/baseline.xlsx
+++ b/experiment/baseline.xlsx
@@ -4,10 +4,10 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12790"/>
+    <workbookView windowWidth="28800" windowHeight="12960"/>
   </bookViews>
   <sheets>
-    <sheet name="baseline_modified" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -47,7 +47,7 @@
     <t>Reprobot</t>
   </si>
   <si>
-    <t>NewPipe-7825</t>
+    <t>Aegis-500</t>
   </si>
   <si>
     <r>
@@ -61,6 +61,756 @@
     </r>
   </si>
   <si>
+    <t>3.30.557</t>
+  </si>
+  <si>
+    <t>Alarmio-47</t>
+  </si>
+  <si>
+    <t>4.53.889</t>
+  </si>
+  <si>
+    <t>1.31.395</t>
+  </si>
+  <si>
+    <t>0.45.897</t>
+  </si>
+  <si>
+    <t>1.26.080</t>
+  </si>
+  <si>
+    <t>13.46.903</t>
+  </si>
+  <si>
+    <t>andOTP-569</t>
+  </si>
+  <si>
+    <t>1.55.607</t>
+  </si>
+  <si>
+    <t>andror2-11</t>
+  </si>
+  <si>
+    <t>0.52.048</t>
+  </si>
+  <si>
+    <t>0.13.761</t>
+  </si>
+  <si>
+    <t>1.02.567</t>
+  </si>
+  <si>
+    <t>0.31.479</t>
+  </si>
+  <si>
+    <t>5.49.730</t>
+  </si>
+  <si>
+    <t>andror2-159</t>
+  </si>
+  <si>
+    <t>andror2-162</t>
+  </si>
+  <si>
+    <t>2.33.880</t>
+  </si>
+  <si>
+    <t>0.52.817</t>
+  </si>
+  <si>
+    <t>andror2-164</t>
+  </si>
+  <si>
+    <t>andror2-168</t>
+  </si>
+  <si>
+    <t>andror2-198</t>
+  </si>
+  <si>
+    <t>1.09.257</t>
+  </si>
+  <si>
+    <t>andror2-23</t>
+  </si>
+  <si>
+    <t>2.29.604</t>
+  </si>
+  <si>
+    <t>0.12.234</t>
+  </si>
+  <si>
+    <t>0.32.708</t>
+  </si>
+  <si>
+    <t>1.06.374</t>
+  </si>
+  <si>
+    <t>4.25.992</t>
+  </si>
+  <si>
+    <t>andror2-276</t>
+  </si>
+  <si>
+    <t>andror2-7</t>
+  </si>
+  <si>
+    <t>4.05.725</t>
+  </si>
+  <si>
+    <t>0.34.502</t>
+  </si>
+  <si>
+    <t>2.25.838</t>
+  </si>
+  <si>
+    <t>anglers-9</t>
+  </si>
+  <si>
+    <t>ankidroid-9914</t>
+  </si>
+  <si>
+    <t>7.42.208</t>
+  </si>
+  <si>
+    <t>4.18.445</t>
+  </si>
+  <si>
+    <t>4.47.051</t>
+  </si>
+  <si>
+    <t>ankidroid-10584</t>
+  </si>
+  <si>
+    <t>ankidroid-2564</t>
+  </si>
+  <si>
+    <t>2.44.019</t>
+  </si>
+  <si>
+    <t>0.51.749</t>
+  </si>
+  <si>
+    <t>ankidroid-2681</t>
+  </si>
+  <si>
+    <t>2.08.827</t>
+  </si>
+  <si>
+    <t>1.56.427</t>
+  </si>
+  <si>
+    <t>ankidroid-2765</t>
+  </si>
+  <si>
+    <t>ankidroid-3224</t>
+  </si>
+  <si>
+    <t>0.21.583</t>
+  </si>
+  <si>
+    <t>ankidroid-3370</t>
+  </si>
+  <si>
+    <t>2.35.055</t>
+  </si>
+  <si>
+    <t>1.47.823</t>
+  </si>
+  <si>
+    <t>1.29.479</t>
+  </si>
+  <si>
+    <t>2.53.712</t>
+  </si>
+  <si>
+    <t>15.06.326</t>
+  </si>
+  <si>
+    <t>AntennaPod-3245</t>
+  </si>
+  <si>
+    <t>2.19.893</t>
+  </si>
+  <si>
+    <t>0.52.137</t>
+  </si>
+  <si>
+    <t>1.22.064</t>
+  </si>
+  <si>
+    <t>2.47.914</t>
+  </si>
+  <si>
+    <t>AnyMemo-422</t>
+  </si>
+  <si>
+    <t>7.29.103</t>
+  </si>
+  <si>
+    <t>3.13.314</t>
+  </si>
+  <si>
+    <t>AnyMemo-440</t>
+  </si>
+  <si>
+    <t>AsciiCam-17</t>
+  </si>
+  <si>
+    <t>ATimeTracker-10</t>
+  </si>
+  <si>
+    <t>2.18.530</t>
+  </si>
+  <si>
+    <t>banderlabs-23</t>
+  </si>
+  <si>
+    <t>5.05.162</t>
+  </si>
+  <si>
+    <t>2.20.189</t>
+  </si>
+  <si>
+    <t>1.28.695</t>
+  </si>
+  <si>
+    <t>4.28.142</t>
+  </si>
+  <si>
+    <t>24.06.732</t>
+  </si>
+  <si>
+    <t>Birthdroid-13</t>
+  </si>
+  <si>
+    <t>3.21.190</t>
+  </si>
+  <si>
+    <t>0.40.967</t>
+  </si>
+  <si>
+    <t>1.06.807</t>
+  </si>
+  <si>
+    <t>2.06.173</t>
+  </si>
+  <si>
+    <t>11.36.734</t>
+  </si>
+  <si>
+    <t>bounty-39073</t>
+  </si>
+  <si>
+    <t>3.58.856</t>
+  </si>
+  <si>
+    <t>2.29.056</t>
+  </si>
+  <si>
+    <t>7.16.762</t>
+  </si>
+  <si>
+    <t>calendula-134</t>
+  </si>
+  <si>
+    <t>collect-1402</t>
+  </si>
+  <si>
+    <t>6.46.094</t>
+  </si>
+  <si>
+    <t>2.46.543</t>
+  </si>
+  <si>
+    <t>2.03.292</t>
+  </si>
+  <si>
+    <t>3.14.063</t>
+  </si>
+  <si>
+    <t>19.29.613</t>
+  </si>
+  <si>
+    <t>collect-2533</t>
+  </si>
+  <si>
+    <t>collect-2993</t>
+  </si>
+  <si>
+    <t>5.11.501</t>
+  </si>
+  <si>
+    <t>0.48.078</t>
+  </si>
+  <si>
+    <t>collect-3529</t>
+  </si>
+  <si>
+    <t>2.02.047</t>
+  </si>
+  <si>
+    <t>0.23.622</t>
+  </si>
+  <si>
+    <t>1.10.984</t>
+  </si>
+  <si>
+    <t>4.18.625</t>
+  </si>
+  <si>
+    <t>17.21.144</t>
+  </si>
+  <si>
+    <t>FakeStandby-30</t>
+  </si>
+  <si>
+    <t>3.41.593</t>
+  </si>
+  <si>
+    <t>FastAdapter-113</t>
+  </si>
+  <si>
+    <t>FastAdapter-394</t>
+  </si>
+  <si>
+    <t>10.20.261</t>
+  </si>
+  <si>
+    <t>0.25.406</t>
+  </si>
+  <si>
+    <t>1.26.284</t>
+  </si>
+  <si>
+    <t>2.24.553</t>
+  </si>
+  <si>
+    <t>20.16.502</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>fastnfitness-142</t>
+  </si>
+  <si>
+    <t>1.26.575</t>
+  </si>
+  <si>
+    <t>2.34.577</t>
+  </si>
+  <si>
+    <t>3.01.839</t>
+  </si>
+  <si>
+    <t>2.24.101</t>
+  </si>
+  <si>
+    <t>Fermi-321</t>
+  </si>
+  <si>
+    <t>1.16.092</t>
+  </si>
+  <si>
+    <t>Field-Book-146</t>
+  </si>
+  <si>
+    <t>5.13.502</t>
+  </si>
+  <si>
+    <t>6.32.565</t>
+  </si>
+  <si>
+    <t>FlashCards-13</t>
+  </si>
+  <si>
+    <t>8.02.324</t>
+  </si>
+  <si>
+    <t>food-tracker-55</t>
+  </si>
+  <si>
+    <t>7.31.040</t>
+  </si>
+  <si>
+    <t>2.37.106</t>
+  </si>
+  <si>
+    <t>gnucash-664</t>
+  </si>
+  <si>
+    <t>11.15.521</t>
+  </si>
+  <si>
+    <t>GrowTracker-87</t>
+  </si>
+  <si>
+    <t>GrowTracker-89</t>
+  </si>
+  <si>
+    <t>IMSI-816</t>
+  </si>
+  <si>
+    <t>0.15.477</t>
+  </si>
+  <si>
+    <t>0.16.188</t>
+  </si>
+  <si>
+    <t>0.01.757</t>
+  </si>
+  <si>
+    <t>0.47.314</t>
+  </si>
+  <si>
+    <t>2.19.251</t>
+  </si>
+  <si>
+    <t>iNaturalistAndroid-722</t>
+  </si>
+  <si>
+    <t>ladybug-129</t>
+  </si>
+  <si>
+    <t>1.42.512</t>
+  </si>
+  <si>
+    <t>ladybug-225</t>
+  </si>
+  <si>
+    <t>2.55.774</t>
+  </si>
+  <si>
+    <t>0.38.074</t>
+  </si>
+  <si>
+    <t>5.35.175</t>
+  </si>
+  <si>
+    <t>LibreNews-23</t>
+  </si>
+  <si>
+    <t>2.18.212</t>
+  </si>
+  <si>
+    <t>1.36.740</t>
+  </si>
+  <si>
+    <t>0.50.672</t>
+  </si>
+  <si>
+    <t>4.11.409</t>
+  </si>
+  <si>
+    <t>23.58.417</t>
+  </si>
+  <si>
+    <t>LibreNews-27</t>
+  </si>
+  <si>
+    <t>3.07.228</t>
+  </si>
+  <si>
+    <t>0.40.742</t>
+  </si>
+  <si>
+    <t>lrkFM-44</t>
+  </si>
+  <si>
+    <t>markor-1565</t>
+  </si>
+  <si>
+    <t>markor-194</t>
+  </si>
+  <si>
+    <t>6.11.305</t>
+  </si>
+  <si>
+    <t>2.31.865</t>
+  </si>
+  <si>
+    <t>2.18.704</t>
+  </si>
+  <si>
+    <t>13.05.746</t>
+  </si>
+  <si>
+    <t>materialistic-1067</t>
+  </si>
+  <si>
+    <t>MBTACA-12</t>
+  </si>
+  <si>
+    <t>1.27.685</t>
+  </si>
+  <si>
+    <t>0.48.693</t>
+  </si>
+  <si>
+    <t>3.19.770</t>
+  </si>
+  <si>
+    <t>Memento-169</t>
+  </si>
+  <si>
+    <t>Mesh-495</t>
+  </si>
+  <si>
+    <t>8.43.507</t>
+  </si>
+  <si>
+    <t>5.15.765</t>
+  </si>
+  <si>
+    <t>21.24.158</t>
+  </si>
+  <si>
+    <t>NewPipe-7825</t>
+  </si>
+  <si>
+    <t>noad-1</t>
+  </si>
+  <si>
+    <t>0.14.072</t>
+  </si>
+  <si>
+    <t>0.13.025</t>
+  </si>
+  <si>
+    <t>0.12.879</t>
+  </si>
+  <si>
+    <t>0.45.019</t>
+  </si>
+  <si>
+    <t>4.53.022</t>
+  </si>
+  <si>
+    <t>toolkit-26</t>
+  </si>
+  <si>
+    <t>2.49.731</t>
+  </si>
+  <si>
+    <t>obd-22</t>
+  </si>
+  <si>
+    <t>7.36.551</t>
+  </si>
+  <si>
+    <t>0.23.204</t>
+  </si>
+  <si>
+    <t>2.31.603</t>
+  </si>
+  <si>
+    <t>Open-Shell-Menu-2024</t>
+  </si>
+  <si>
+    <t>12.23.918</t>
+  </si>
+  <si>
+    <t>pedometer-101</t>
+  </si>
+  <si>
+    <t>6.04.819</t>
+  </si>
+  <si>
+    <t>0.46.021</t>
+  </si>
+  <si>
+    <t>plusTimer-19</t>
+  </si>
+  <si>
+    <t>0.13.275</t>
+  </si>
+  <si>
+    <t>0.17.419</t>
+  </si>
+  <si>
+    <t>0.19.174</t>
+  </si>
+  <si>
+    <t>0.51.937</t>
+  </si>
+  <si>
+    <t>2.16.760</t>
+  </si>
+  <si>
+    <t>qksms-482</t>
+  </si>
+  <si>
+    <t>10.01.028</t>
+  </si>
+  <si>
+    <t>qksms-585</t>
+  </si>
+  <si>
+    <t>1.17.487</t>
+  </si>
+  <si>
+    <t>2.12.583</t>
+  </si>
+  <si>
+    <t>recdroid-1</t>
+  </si>
+  <si>
+    <t>5.04.542</t>
+  </si>
+  <si>
+    <t>0.45.041</t>
+  </si>
+  <si>
+    <t>1.21.926</t>
+  </si>
+  <si>
+    <t>2.03.277</t>
+  </si>
+  <si>
+    <t>16.29.258</t>
+  </si>
+  <si>
+    <t>recdroid-13</t>
+  </si>
+  <si>
+    <t>2.09.522</t>
+  </si>
+  <si>
+    <t>0.33.679</t>
+  </si>
+  <si>
+    <t>1.31.550</t>
+  </si>
+  <si>
+    <t>2.19.057</t>
+  </si>
+  <si>
+    <t>19.21.430</t>
+  </si>
+  <si>
+    <t>recdroid-17</t>
+  </si>
+  <si>
+    <t>1.23.523</t>
+  </si>
+  <si>
+    <t>recdroid-23</t>
+  </si>
+  <si>
+    <t>recdroid-30</t>
+  </si>
+  <si>
+    <t>2.30.697</t>
+  </si>
+  <si>
+    <t>1.26.898</t>
+  </si>
+  <si>
+    <t>1.32.814</t>
+  </si>
+  <si>
+    <t>2.13.057</t>
+  </si>
+  <si>
+    <t>14.23.214</t>
+  </si>
+  <si>
+    <t>recdroid-49</t>
+  </si>
+  <si>
+    <t>recdroid-5</t>
+  </si>
+  <si>
+    <t>recdroid-58</t>
+  </si>
+  <si>
+    <t>1.28.741</t>
+  </si>
+  <si>
+    <t>0.24.272</t>
+  </si>
+  <si>
+    <t>0.47.112</t>
+  </si>
+  <si>
+    <t>1.17.243</t>
+  </si>
+  <si>
+    <t>9.37.431</t>
+  </si>
+  <si>
+    <t>recdroid-64</t>
+  </si>
+  <si>
+    <t>1.33.617</t>
+  </si>
+  <si>
+    <t>1.17.513</t>
+  </si>
+  <si>
+    <t>1.08.406</t>
+  </si>
+  <si>
+    <t>1.43.842</t>
+  </si>
+  <si>
+    <t>16.58.639</t>
+  </si>
+  <si>
+    <t>recdroid-7</t>
+  </si>
+  <si>
+    <t>1.47.461</t>
+  </si>
+  <si>
+    <t>0.27.403</t>
+  </si>
+  <si>
+    <t>1.47.214</t>
+  </si>
+  <si>
+    <t>3.41.394</t>
+  </si>
+  <si>
+    <t>27.42.616</t>
+  </si>
+  <si>
+    <t>record-1</t>
+  </si>
+  <si>
+    <t>revolution-irc-183</t>
+  </si>
+  <si>
+    <t>9.21.976</t>
+  </si>
+  <si>
+    <t>5.21.356</t>
+  </si>
+  <si>
+    <t>9.36.157</t>
+  </si>
+  <si>
+    <t>saner2022-1207</t>
+  </si>
+  <si>
+    <t>1.24.699</t>
+  </si>
+  <si>
+    <t>1.57.485</t>
+  </si>
+  <si>
+    <t>3.32.849</t>
+  </si>
+  <si>
+    <t>saner2022-23</t>
+  </si>
+  <si>
+    <t>5.19.409</t>
+  </si>
+  <si>
+    <t>1.58.626</t>
+  </si>
+  <si>
     <t>sdbviewer-10</t>
   </si>
   <si>
@@ -79,100 +829,79 @@
     <t>14.47.942</t>
   </si>
   <si>
-    <t>Anki-Android-9914</t>
-  </si>
-  <si>
-    <t>7.42.208</t>
-  </si>
-  <si>
-    <t>4.18.445</t>
-  </si>
-  <si>
-    <t>4.47.051</t>
-  </si>
-  <si>
-    <t>ankidroid-10584</t>
-  </si>
-  <si>
-    <t>Alarmio-47</t>
-  </si>
-  <si>
-    <t>4.53.889</t>
-  </si>
-  <si>
-    <t>1.31.395</t>
-  </si>
-  <si>
-    <t>0.45.897</t>
-  </si>
-  <si>
-    <t>1.26.080</t>
-  </si>
-  <si>
-    <t>13.46.903</t>
-  </si>
-  <si>
-    <t>plusTimer-19</t>
-  </si>
-  <si>
-    <t>0.13.275</t>
-  </si>
-  <si>
-    <t>0.17.419</t>
-  </si>
-  <si>
-    <t>0.19.174</t>
-  </si>
-  <si>
-    <t>0.51.937</t>
-  </si>
-  <si>
-    <t>2.16.760</t>
-  </si>
-  <si>
-    <t>GrowTracker-89</t>
+    <t>sdbviewer-7</t>
   </si>
   <si>
     <t>Shuttle-456</t>
   </si>
   <si>
-    <t>ankidroid-3370</t>
-  </si>
-  <si>
-    <t>2.35.055</t>
-  </si>
-  <si>
-    <t>1.47.823</t>
-  </si>
-  <si>
-    <t>1.29.479</t>
-  </si>
-  <si>
-    <t>2.53.712</t>
-  </si>
-  <si>
-    <t>15.06.326</t>
-  </si>
-  <si>
-    <t>ankidroid-2765</t>
-  </si>
-  <si>
-    <t>ankidroid-2564</t>
-  </si>
-  <si>
-    <t>2.44.019</t>
-  </si>
-  <si>
-    <t>0.51.749</t>
-  </si>
-  <si>
-    <t>ankidroid-2681</t>
-  </si>
-  <si>
-    <t>2.08.827</t>
-  </si>
-  <si>
-    <t>1.56.427</t>
+    <t>SimpleJoinMessage-3</t>
+  </si>
+  <si>
+    <t>3.34.890</t>
+  </si>
+  <si>
+    <t>0.53.337</t>
+  </si>
+  <si>
+    <t>2.08.970</t>
+  </si>
+  <si>
+    <t>3.34.518</t>
+  </si>
+  <si>
+    <t>5.49.172</t>
+  </si>
+  <si>
+    <t>TagMo-12</t>
+  </si>
+  <si>
+    <t>0.41.178</t>
+  </si>
+  <si>
+    <t>1.51.438</t>
+  </si>
+  <si>
+    <t>2.41.760</t>
+  </si>
+  <si>
+    <t>2.31.891</t>
+  </si>
+  <si>
+    <t>13.14.164</t>
+  </si>
+  <si>
+    <t>thunderbird-2612</t>
+  </si>
+  <si>
+    <t>9.17.985</t>
+  </si>
+  <si>
+    <t>thunderbird-3255</t>
+  </si>
+  <si>
+    <t>2.09.827</t>
+  </si>
+  <si>
+    <t>0.59.017</t>
+  </si>
+  <si>
+    <t>1.16.955</t>
+  </si>
+  <si>
+    <t>2.57.746</t>
+  </si>
+  <si>
+    <t>Trainer-7</t>
+  </si>
+  <si>
+    <t>3.12.773</t>
+  </si>
+  <si>
+    <t>9.45.421</t>
+  </si>
+  <si>
+    <t>trickytripper-43</t>
   </si>
   <si>
     <t>WhereYouGo-368</t>
@@ -191,735 +920,6 @@
   </si>
   <si>
     <t>24.29.775</t>
-  </si>
-  <si>
-    <t>food-tracker-55</t>
-  </si>
-  <si>
-    <t>7.31.040</t>
-  </si>
-  <si>
-    <t>2.37.106</t>
-  </si>
-  <si>
-    <t>GrowTracker-87</t>
-  </si>
-  <si>
-    <t>markor-1565</t>
-  </si>
-  <si>
-    <t>Mesh-495</t>
-  </si>
-  <si>
-    <t>8.43.507</t>
-  </si>
-  <si>
-    <t>5.15.765</t>
-  </si>
-  <si>
-    <t>21.24.158</t>
-  </si>
-  <si>
-    <t>sdbviewer-7</t>
-  </si>
-  <si>
-    <t>FakeStandby-30</t>
-  </si>
-  <si>
-    <t>3.41.593</t>
-  </si>
-  <si>
-    <t>revolution-irc-183</t>
-  </si>
-  <si>
-    <t>9.21.976</t>
-  </si>
-  <si>
-    <t>5.21.356</t>
-  </si>
-  <si>
-    <t>9.36.157</t>
-  </si>
-  <si>
-    <t>ankidroid-3224</t>
-  </si>
-  <si>
-    <t>0.21.583</t>
-  </si>
-  <si>
-    <t>pedometer-101</t>
-  </si>
-  <si>
-    <t>6.04.819</t>
-  </si>
-  <si>
-    <t>0.46.021</t>
-  </si>
-  <si>
-    <t>andror2-7</t>
-  </si>
-  <si>
-    <t>4.05.725</t>
-  </si>
-  <si>
-    <t>0.34.502</t>
-  </si>
-  <si>
-    <t>2.25.838</t>
-  </si>
-  <si>
-    <t>andror2-11</t>
-  </si>
-  <si>
-    <t>0.52.048</t>
-  </si>
-  <si>
-    <t>0.13.761</t>
-  </si>
-  <si>
-    <t>1.02.567</t>
-  </si>
-  <si>
-    <t>0.31.479</t>
-  </si>
-  <si>
-    <t>5.49.730</t>
-  </si>
-  <si>
-    <t>andror2-23</t>
-  </si>
-  <si>
-    <t>2.29.604</t>
-  </si>
-  <si>
-    <t>0.12.234</t>
-  </si>
-  <si>
-    <t>0.32.708</t>
-  </si>
-  <si>
-    <t>1.06.374</t>
-  </si>
-  <si>
-    <t>4.25.992</t>
-  </si>
-  <si>
-    <t>andror2-159</t>
-  </si>
-  <si>
-    <t>andror2-162</t>
-  </si>
-  <si>
-    <t>2.33.880</t>
-  </si>
-  <si>
-    <t>0.52.817</t>
-  </si>
-  <si>
-    <t>andror2-164</t>
-  </si>
-  <si>
-    <t>andror2-168</t>
-  </si>
-  <si>
-    <t>andror2-198</t>
-  </si>
-  <si>
-    <t>1.09.257</t>
-  </si>
-  <si>
-    <t>andror2-276</t>
-  </si>
-  <si>
-    <t>recdroid-1</t>
-  </si>
-  <si>
-    <t>5.04.542</t>
-  </si>
-  <si>
-    <t>0.45.041</t>
-  </si>
-  <si>
-    <t>1.21.926</t>
-  </si>
-  <si>
-    <t>2.03.277</t>
-  </si>
-  <si>
-    <t>16.29.258</t>
-  </si>
-  <si>
-    <t>recdroid-2</t>
-  </si>
-  <si>
-    <t>6.11.305</t>
-  </si>
-  <si>
-    <t>2.31.865</t>
-  </si>
-  <si>
-    <t>2.18.704</t>
-  </si>
-  <si>
-    <t>13.05.746</t>
-  </si>
-  <si>
-    <t>recdroid-3</t>
-  </si>
-  <si>
-    <t>3.21.190</t>
-  </si>
-  <si>
-    <t>0.40.967</t>
-  </si>
-  <si>
-    <t>1.06.807</t>
-  </si>
-  <si>
-    <t>2.06.173</t>
-  </si>
-  <si>
-    <t>11.36.734</t>
-  </si>
-  <si>
-    <t>recdroid-5</t>
-  </si>
-  <si>
-    <t>recdroid-7</t>
-  </si>
-  <si>
-    <t>1.47.461</t>
-  </si>
-  <si>
-    <t>0.27.403</t>
-  </si>
-  <si>
-    <t>1.47.214</t>
-  </si>
-  <si>
-    <t>3.41.394</t>
-  </si>
-  <si>
-    <t>27.42.616</t>
-  </si>
-  <si>
-    <t>recdroid-8</t>
-  </si>
-  <si>
-    <t>recdroid-9</t>
-  </si>
-  <si>
-    <t>5.05.162</t>
-  </si>
-  <si>
-    <t>2.20.189</t>
-  </si>
-  <si>
-    <t>1.28.695</t>
-  </si>
-  <si>
-    <t>4.28.142</t>
-  </si>
-  <si>
-    <t>24.06.732</t>
-  </si>
-  <si>
-    <t>recdroid-11</t>
-  </si>
-  <si>
-    <t>1.16.092</t>
-  </si>
-  <si>
-    <t>recdroid-12</t>
-  </si>
-  <si>
-    <t>10.20.261</t>
-  </si>
-  <si>
-    <t>0.25.406</t>
-  </si>
-  <si>
-    <t>1.26.284</t>
-  </si>
-  <si>
-    <t>2.24.553</t>
-  </si>
-  <si>
-    <t>20.16.502</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
-  </si>
-  <si>
-    <t>recdroid-13</t>
-  </si>
-  <si>
-    <t>2.09.522</t>
-  </si>
-  <si>
-    <t>0.33.679</t>
-  </si>
-  <si>
-    <t>1.31.550</t>
-  </si>
-  <si>
-    <t>2.19.057</t>
-  </si>
-  <si>
-    <t>19.21.430</t>
-  </si>
-  <si>
-    <t>recdroid-14</t>
-  </si>
-  <si>
-    <t>2.18.212</t>
-  </si>
-  <si>
-    <t>1.36.740</t>
-  </si>
-  <si>
-    <t>0.50.672</t>
-  </si>
-  <si>
-    <t>4.11.409</t>
-  </si>
-  <si>
-    <t>23.58.417</t>
-  </si>
-  <si>
-    <t>recdroid-15</t>
-  </si>
-  <si>
-    <t>3.07.228</t>
-  </si>
-  <si>
-    <t>0.40.742</t>
-  </si>
-  <si>
-    <t>recdroid-17</t>
-  </si>
-  <si>
-    <t>1.23.523</t>
-  </si>
-  <si>
-    <t>recdroid-21</t>
-  </si>
-  <si>
-    <t>1.27.685</t>
-  </si>
-  <si>
-    <t>0.48.693</t>
-  </si>
-  <si>
-    <t>3.19.770</t>
-  </si>
-  <si>
-    <t>recdroid-23</t>
-  </si>
-  <si>
-    <t>recdroid-24</t>
-  </si>
-  <si>
-    <t>7.36.551</t>
-  </si>
-  <si>
-    <t>0.23.204</t>
-  </si>
-  <si>
-    <t>2.31.603</t>
-  </si>
-  <si>
-    <t>recdroid-25</t>
-  </si>
-  <si>
-    <t>recdroid-26</t>
-  </si>
-  <si>
-    <t>2.02.047</t>
-  </si>
-  <si>
-    <t>0.23.622</t>
-  </si>
-  <si>
-    <t>1.10.984</t>
-  </si>
-  <si>
-    <t>4.18.625</t>
-  </si>
-  <si>
-    <t>17.21.144</t>
-  </si>
-  <si>
-    <t>recdroid-27</t>
-  </si>
-  <si>
-    <t>2.09.827</t>
-  </si>
-  <si>
-    <t>0.59.017</t>
-  </si>
-  <si>
-    <t>1.16.955</t>
-  </si>
-  <si>
-    <t>2.57.746</t>
-  </si>
-  <si>
-    <t>recdroid-28</t>
-  </si>
-  <si>
-    <t>9.17.985</t>
-  </si>
-  <si>
-    <t>recdroid-29</t>
-  </si>
-  <si>
-    <t>2.49.731</t>
-  </si>
-  <si>
-    <t>recdroid-30</t>
-  </si>
-  <si>
-    <t>2.30.697</t>
-  </si>
-  <si>
-    <t>1.26.898</t>
-  </si>
-  <si>
-    <t>1.32.814</t>
-  </si>
-  <si>
-    <t>2.13.057</t>
-  </si>
-  <si>
-    <t>14.23.214</t>
-  </si>
-  <si>
-    <t>recdroid-31</t>
-  </si>
-  <si>
-    <t>0.41.178</t>
-  </si>
-  <si>
-    <t>1.51.438</t>
-  </si>
-  <si>
-    <t>2.41.760</t>
-  </si>
-  <si>
-    <t>2.31.891</t>
-  </si>
-  <si>
-    <t>13.14.164</t>
-  </si>
-  <si>
-    <t>recdroid-33</t>
-  </si>
-  <si>
-    <t>8.02.324</t>
-  </si>
-  <si>
-    <t>recdroid-34</t>
-  </si>
-  <si>
-    <t>recdroid-35</t>
-  </si>
-  <si>
-    <t>recdroid-38</t>
-  </si>
-  <si>
-    <t>0.15.477</t>
-  </si>
-  <si>
-    <t>0.16.188</t>
-  </si>
-  <si>
-    <t>0.01.757</t>
-  </si>
-  <si>
-    <t>0.47.314</t>
-  </si>
-  <si>
-    <t>2.19.251</t>
-  </si>
-  <si>
-    <t>recdroid-39</t>
-  </si>
-  <si>
-    <t>recdroid-42</t>
-  </si>
-  <si>
-    <t>1.17.487</t>
-  </si>
-  <si>
-    <t>2.12.583</t>
-  </si>
-  <si>
-    <t>recdroid-45</t>
-  </si>
-  <si>
-    <t>recdroid-49</t>
-  </si>
-  <si>
-    <t>recdroid-53</t>
-  </si>
-  <si>
-    <t>6.46.094</t>
-  </si>
-  <si>
-    <t>2.46.543</t>
-  </si>
-  <si>
-    <t>2.03.292</t>
-  </si>
-  <si>
-    <t>3.14.063</t>
-  </si>
-  <si>
-    <t>19.29.613</t>
-  </si>
-  <si>
-    <t>recdroid-55</t>
-  </si>
-  <si>
-    <t>recdroid-56</t>
-  </si>
-  <si>
-    <t>12.23.918</t>
-  </si>
-  <si>
-    <t>recdroid-57</t>
-  </si>
-  <si>
-    <t>7.29.103</t>
-  </si>
-  <si>
-    <t>3.13.314</t>
-  </si>
-  <si>
-    <t>recdroid-58</t>
-  </si>
-  <si>
-    <t>1.28.741</t>
-  </si>
-  <si>
-    <t>0.24.272</t>
-  </si>
-  <si>
-    <t>0.47.112</t>
-  </si>
-  <si>
-    <t>1.17.243</t>
-  </si>
-  <si>
-    <t>9.37.431</t>
-  </si>
-  <si>
-    <t>recdroid-60</t>
-  </si>
-  <si>
-    <t>5.11.501</t>
-  </si>
-  <si>
-    <t>0.48.078</t>
-  </si>
-  <si>
-    <t>recdroid-61</t>
-  </si>
-  <si>
-    <t>3.58.856</t>
-  </si>
-  <si>
-    <t>2.29.056</t>
-  </si>
-  <si>
-    <t>7.16.762</t>
-  </si>
-  <si>
-    <t>recdroid-62</t>
-  </si>
-  <si>
-    <t>2.18.530</t>
-  </si>
-  <si>
-    <t>recdroid-64</t>
-  </si>
-  <si>
-    <t>1.33.617</t>
-  </si>
-  <si>
-    <t>1.17.513</t>
-  </si>
-  <si>
-    <t>1.08.406</t>
-  </si>
-  <si>
-    <t>1.43.842</t>
-  </si>
-  <si>
-    <t>16.58.639</t>
-  </si>
-  <si>
-    <t>saner2022-2</t>
-  </si>
-  <si>
-    <t>2.55.774</t>
-  </si>
-  <si>
-    <t>0.38.074</t>
-  </si>
-  <si>
-    <t>5.35.175</t>
-  </si>
-  <si>
-    <t>saner2022-8</t>
-  </si>
-  <si>
-    <t>saner2022-11</t>
-  </si>
-  <si>
-    <t>0.14.072</t>
-  </si>
-  <si>
-    <t>0.13.025</t>
-  </si>
-  <si>
-    <t>0.12.879</t>
-  </si>
-  <si>
-    <t>0.45.019</t>
-  </si>
-  <si>
-    <t>4.53.022</t>
-  </si>
-  <si>
-    <t>saner2022-18</t>
-  </si>
-  <si>
-    <t>saner2022-23</t>
-  </si>
-  <si>
-    <t>5.19.409</t>
-  </si>
-  <si>
-    <t>1.58.626</t>
-  </si>
-  <si>
-    <t>saner2022-129</t>
-  </si>
-  <si>
-    <t>1.42.512</t>
-  </si>
-  <si>
-    <t>saner2022-271</t>
-  </si>
-  <si>
-    <t>3.30.557</t>
-  </si>
-  <si>
-    <t>saner2022-1089</t>
-  </si>
-  <si>
-    <t>3.34.890</t>
-  </si>
-  <si>
-    <t>0.53.337</t>
-  </si>
-  <si>
-    <t>2.08.970</t>
-  </si>
-  <si>
-    <t>3.34.518</t>
-  </si>
-  <si>
-    <t>5.49.172</t>
-  </si>
-  <si>
-    <t>saner2022-1096</t>
-  </si>
-  <si>
-    <t>saner2022-1133</t>
-  </si>
-  <si>
-    <t>2.19.893</t>
-  </si>
-  <si>
-    <t>0.52.137</t>
-  </si>
-  <si>
-    <t>1.22.064</t>
-  </si>
-  <si>
-    <t>2.47.914</t>
-  </si>
-  <si>
-    <t>saner2022-1160</t>
-  </si>
-  <si>
-    <t>10.01.028</t>
-  </si>
-  <si>
-    <t>saner2022-1207</t>
-  </si>
-  <si>
-    <t>1.24.699</t>
-  </si>
-  <si>
-    <t>1.57.485</t>
-  </si>
-  <si>
-    <t>3.32.849</t>
-  </si>
-  <si>
-    <t>saner2022-1215</t>
-  </si>
-  <si>
-    <t>1.55.607</t>
-  </si>
-  <si>
-    <t>saner2022-1227</t>
-  </si>
-  <si>
-    <t>11.15.521</t>
-  </si>
-  <si>
-    <t>saner2022-1299</t>
-  </si>
-  <si>
-    <t>5.13.502</t>
-  </si>
-  <si>
-    <t>6.32.565</t>
-  </si>
-  <si>
-    <t>saner2022-1430</t>
-  </si>
-  <si>
-    <t>1.26.575</t>
-  </si>
-  <si>
-    <t>2.34.577</t>
-  </si>
-  <si>
-    <t>3.01.839</t>
-  </si>
-  <si>
-    <t>2.24.101</t>
-  </si>
-  <si>
-    <t>saner2022-1447</t>
-  </si>
-  <si>
-    <t>saner2022-1568</t>
-  </si>
-  <si>
-    <t>saner2022-1645</t>
-  </si>
-  <si>
-    <t>3.12.773</t>
-  </si>
-  <si>
-    <t>9.45.421</t>
   </si>
   <si>
     <t>yakusu-1</t>
@@ -953,7 +953,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -962,6 +962,13 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
@@ -1312,12 +1319,40 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="11">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1420,9 +1455,7 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -1438,142 +1471,147 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
+  <cellXfs count="5">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1627,221 +1665,7 @@
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="17">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="double">
-          <color theme="4"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4"/>
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <border>
-        <left style="thin">
-          <color theme="4"/>
-        </left>
-        <right style="thin">
-          <color theme="4"/>
-        </right>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-        <horizontal style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-  </dxfs>
-  <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
-    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="6"/>
-      <tableStyleElement type="headerRow" dxfId="5"/>
-      <tableStyleElement type="totalRow" dxfId="4"/>
-      <tableStyleElement type="firstColumn" dxfId="3"/>
-      <tableStyleElement type="lastColumn" dxfId="2"/>
-      <tableStyleElement type="firstRowStripe" dxfId="1"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
-    </tableStyle>
-    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="16"/>
-      <tableStyleElement type="totalRow" dxfId="15"/>
-      <tableStyleElement type="firstRowStripe" dxfId="14"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
-      <tableStyleElement type="pageFieldValues" dxfId="7"/>
-    </tableStyle>
-  </tableStyles>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1851,7 +1675,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -1861,39 +1685,39 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1925,7 +1749,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -1960,7 +1783,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -1972,131 +1794,160 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="35000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="80000">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="40000">
               <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
@@ -2109,38 +1960,42 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:J94"/>
-  <sheetFormatPr defaultColWidth="9.81818181818182" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="21.6363636363636" style="1" customWidth="1"/>
-    <col min="2" max="2" width="15.9090909090909" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15.6363636363636" style="1" customWidth="1"/>
-    <col min="4" max="4" width="13.5454545454545" style="1" customWidth="1"/>
-    <col min="5" max="5" width="11.9090909090909" style="1" customWidth="1"/>
-    <col min="6" max="6" width="12" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="9.81818181818182" style="1"/>
+    <col min="1" max="1" width="34.1833333333333" style="1" customWidth="1"/>
+    <col min="2" max="2" width="14.1833333333333" style="1" customWidth="1"/>
+    <col min="3" max="3" width="16.0916666666667" style="1" customWidth="1"/>
+    <col min="4" max="4" width="13.3666666666667" style="1" customWidth="1"/>
+    <col min="5" max="5" width="14" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.275" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:10">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6">
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+    </row>
+    <row r="2" spans="1:10">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
@@ -2151,7 +2006,7 @@
         <v>7</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>7</v>
@@ -2160,269 +2015,269 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:10">
       <c r="A3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
       <c r="A4" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F4" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="1" t="s">
+      <c r="B5" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>7</v>
-      </c>
       <c r="C5" s="1" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
       <c r="A6" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="F6" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" s="1" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="1" t="s">
+      <c r="B7" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="C7" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="D7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="B8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="B9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="B10" s="1" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="1" t="s">
+      <c r="C10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="1" t="s">
+      <c r="B11" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="1" t="s">
+      <c r="C11" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="D11" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="E11" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="F11" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="E10" s="1" t="s">
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="B12" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" s="1" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="1" t="s">
+      <c r="B13" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B11" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="1" t="s">
+      <c r="C13" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="D13" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="E13" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D12" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="1" t="s">
+      <c r="B14" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B15" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="C15" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D15" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D13" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="1" t="s">
+      <c r="E15" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="F15" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" s="1" t="s">
         <v>47</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="1" t="s">
-        <v>55</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>7</v>
@@ -2442,13 +2297,13 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="1" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>7</v>
+        <v>49</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>7</v>
+        <v>50</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>7</v>
@@ -2462,13 +2317,13 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="1" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>7</v>
@@ -2477,12 +2332,12 @@
         <v>7</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>60</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="1" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>7</v>
@@ -2502,10 +2357,10 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="1" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>7</v>
@@ -2522,56 +2377,56 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="1" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>7</v>
+        <v>61</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>7</v>
+        <v>62</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="1" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>7</v>
+        <v>65</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>7</v>
+        <v>66</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>7</v>
+        <v>67</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D23" s="1" t="s">
         <v>70</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>7</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>7</v>
@@ -2582,16 +2437,16 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>74</v>
+        <v>7</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>75</v>
+        <v>7</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>76</v>
+        <v>7</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>7</v>
@@ -2602,93 +2457,93 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="1" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>78</v>
+        <v>7</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>79</v>
+        <v>7</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>80</v>
+        <v>7</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>81</v>
+        <v>7</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>82</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="1" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>84</v>
+        <v>7</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>85</v>
+        <v>7</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>87</v>
+        <v>7</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>88</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="1" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>7</v>
+        <v>76</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>7</v>
+        <v>77</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>7</v>
+        <v>78</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>7</v>
+        <v>79</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>7</v>
+        <v>80</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="1" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>7</v>
+        <v>84</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>7</v>
+        <v>85</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>7</v>
+        <v>86</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="1" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>7</v>
+        <v>88</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>7</v>
+        <v>89</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>7</v>
@@ -2697,12 +2552,12 @@
         <v>7</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>7</v>
+        <v>90</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="1" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>7</v>
@@ -2722,27 +2577,27 @@
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D31" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="B31" s="1" t="s">
+      <c r="E31" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="C31" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>7</v>
-      </c>
       <c r="F31" s="1" t="s">
-        <v>7</v>
+        <v>97</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>7</v>
@@ -2762,67 +2617,67 @@
     </row>
     <row r="33" spans="1:10">
       <c r="A33" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>101</v>
+        <v>7</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>102</v>
+        <v>7</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>103</v>
+        <v>7</v>
       </c>
     </row>
     <row r="34" spans="1:10">
       <c r="A34" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C34" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="B34" s="1" t="s">
+      <c r="D34" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="C34" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D34" s="1" t="s">
+      <c r="E34" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="E34" s="1" t="s">
+      <c r="F34" s="1" t="s">
         <v>107</v>
-      </c>
-      <c r="F34" s="1" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="35" spans="1:10">
       <c r="A35" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B35" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="B35" s="1" t="s">
-        <v>110</v>
-      </c>
       <c r="C35" s="1" t="s">
-        <v>111</v>
+        <v>7</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>112</v>
+        <v>7</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>113</v>
+        <v>7</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>114</v>
+        <v>7</v>
       </c>
     </row>
     <row r="36" spans="1:10">
       <c r="A36" s="1" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>7</v>
@@ -2842,39 +2697,42 @@
     </row>
     <row r="37" spans="1:10">
       <c r="A37" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F37" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="B37" s="1" t="s">
+      <c r="J37" s="1" t="s">
         <v>117</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="E37" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="F37" s="1" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="38" spans="1:10">
       <c r="A38" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="E38" s="1" t="s">
         <v>122</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E38" s="1" t="s">
-        <v>7</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>7</v>
@@ -2888,27 +2746,27 @@
         <v>124</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>125</v>
+        <v>7</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>126</v>
+        <v>7</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>127</v>
+        <v>7</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>128</v>
+        <v>7</v>
       </c>
     </row>
     <row r="40" spans="1:10">
       <c r="A40" s="1" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>7</v>
+        <v>127</v>
       </c>
       <c r="D40" s="1" t="s">
         <v>7</v>
@@ -2922,76 +2780,73 @@
     </row>
     <row r="41" spans="1:10">
       <c r="A41" s="1" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>133</v>
+        <v>7</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>134</v>
+        <v>7</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>135</v>
+        <v>7</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="J41" s="1" t="s">
-        <v>137</v>
+        <v>7</v>
       </c>
     </row>
     <row r="42" spans="1:10">
       <c r="A42" s="1" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>141</v>
+        <v>7</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>142</v>
+        <v>7</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>143</v>
+        <v>7</v>
       </c>
     </row>
     <row r="43" spans="1:10">
       <c r="A43" s="1" t="s">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>146</v>
+        <v>7</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>147</v>
+        <v>7</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>148</v>
+        <v>7</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>149</v>
+        <v>7</v>
       </c>
     </row>
     <row r="44" spans="1:10">
       <c r="A44" s="1" t="s">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>151</v>
+        <v>7</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>152</v>
+        <v>7</v>
       </c>
       <c r="D44" s="1" t="s">
         <v>7</v>
@@ -3005,10 +2860,10 @@
     </row>
     <row r="45" spans="1:10">
       <c r="A45" s="1" t="s">
-        <v>153</v>
+        <v>136</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>154</v>
+        <v>7</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>7</v>
@@ -3025,27 +2880,27 @@
     </row>
     <row r="46" spans="1:10">
       <c r="A46" s="1" t="s">
-        <v>155</v>
+        <v>137</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>156</v>
+        <v>138</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>7</v>
+        <v>139</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>157</v>
+        <v>140</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>158</v>
+        <v>141</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>7</v>
+        <v>142</v>
       </c>
     </row>
     <row r="47" spans="1:10">
       <c r="A47" s="1" t="s">
-        <v>159</v>
+        <v>143</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>7</v>
@@ -3065,19 +2920,19 @@
     </row>
     <row r="48" spans="1:10">
       <c r="A48" s="1" t="s">
-        <v>160</v>
+        <v>144</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>161</v>
+        <v>7</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>162</v>
+        <v>145</v>
       </c>
       <c r="D48" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>163</v>
+        <v>7</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>7</v>
@@ -3085,13 +2940,13 @@
     </row>
     <row r="49" spans="1:6">
       <c r="A49" s="1" t="s">
-        <v>164</v>
+        <v>146</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>7</v>
+        <v>147</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>7</v>
+        <v>148</v>
       </c>
       <c r="D49" s="1" t="s">
         <v>7</v>
@@ -3100,44 +2955,44 @@
         <v>7</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>7</v>
+        <v>149</v>
       </c>
     </row>
     <row r="50" spans="1:6">
       <c r="A50" s="1" t="s">
-        <v>165</v>
+        <v>150</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>166</v>
+        <v>151</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>168</v>
+        <v>153</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>170</v>
+        <v>155</v>
       </c>
     </row>
     <row r="51" spans="1:6">
       <c r="A51" s="1" t="s">
-        <v>171</v>
+        <v>156</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>172</v>
+        <v>157</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>173</v>
+        <v>158</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>174</v>
+        <v>7</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>175</v>
+        <v>7</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>7</v>
@@ -3145,10 +3000,10 @@
     </row>
     <row r="52" spans="1:6">
       <c r="A52" s="1" t="s">
-        <v>176</v>
+        <v>159</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>177</v>
+        <v>7</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>7</v>
@@ -3165,10 +3020,10 @@
     </row>
     <row r="53" spans="1:6">
       <c r="A53" s="1" t="s">
-        <v>178</v>
+        <v>160</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>179</v>
+        <v>7</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>7</v>
@@ -3185,59 +3040,59 @@
     </row>
     <row r="54" spans="1:6">
       <c r="A54" s="1" t="s">
-        <v>180</v>
+        <v>161</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>181</v>
+        <v>162</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>182</v>
+        <v>7</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>183</v>
+        <v>163</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>184</v>
+        <v>164</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>185</v>
+        <v>165</v>
       </c>
     </row>
     <row r="55" spans="1:6">
       <c r="A55" s="1" t="s">
-        <v>186</v>
+        <v>166</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>187</v>
+        <v>7</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>188</v>
+        <v>7</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>189</v>
+        <v>7</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>190</v>
+        <v>7</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>191</v>
+        <v>7</v>
       </c>
     </row>
     <row r="56" spans="1:6">
       <c r="A56" s="1" t="s">
-        <v>192</v>
+        <v>167</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>193</v>
+        <v>168</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>7</v>
+        <v>169</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>7</v>
+        <v>170</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>7</v>
@@ -3245,7 +3100,7 @@
     </row>
     <row r="57" spans="1:6">
       <c r="A57" s="1" t="s">
-        <v>194</v>
+        <v>171</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>7</v>
@@ -3265,13 +3120,13 @@
     </row>
     <row r="58" spans="1:6">
       <c r="A58" s="1" t="s">
-        <v>195</v>
+        <v>172</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>7</v>
+        <v>173</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>7</v>
+        <v>174</v>
       </c>
       <c r="D58" s="1" t="s">
         <v>7</v>
@@ -3280,64 +3135,64 @@
         <v>7</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>7</v>
+        <v>175</v>
       </c>
     </row>
     <row r="59" spans="1:6">
       <c r="A59" s="1" t="s">
-        <v>196</v>
+        <v>176</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>197</v>
+        <v>7</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>198</v>
+        <v>7</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>199</v>
+        <v>7</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>200</v>
+        <v>7</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>201</v>
+        <v>7</v>
       </c>
     </row>
     <row r="60" spans="1:6">
       <c r="A60" s="1" t="s">
-        <v>202</v>
+        <v>177</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>7</v>
+        <v>178</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>7</v>
+        <v>179</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>7</v>
+        <v>180</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>7</v>
+        <v>181</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>7</v>
+        <v>182</v>
       </c>
     </row>
     <row r="61" spans="1:6">
       <c r="A61" s="1" t="s">
-        <v>203</v>
+        <v>183</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>7</v>
+        <v>184</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>204</v>
+        <v>7</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>205</v>
+        <v>7</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>7</v>
@@ -3345,19 +3200,19 @@
     </row>
     <row r="62" spans="1:6">
       <c r="A62" s="1" t="s">
-        <v>206</v>
+        <v>185</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>7</v>
+        <v>186</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>7</v>
+        <v>187</v>
       </c>
       <c r="D62" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>7</v>
+        <v>188</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>7</v>
@@ -3365,10 +3220,10 @@
     </row>
     <row r="63" spans="1:6">
       <c r="A63" s="1" t="s">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>7</v>
+        <v>190</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>7</v>
@@ -3385,50 +3240,50 @@
     </row>
     <row r="64" spans="1:6">
       <c r="A64" s="1" t="s">
-        <v>208</v>
+        <v>191</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>209</v>
+        <v>192</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>210</v>
+        <v>193</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>211</v>
+        <v>7</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>212</v>
+        <v>7</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>213</v>
+        <v>7</v>
       </c>
     </row>
     <row r="65" spans="1:6">
       <c r="A65" s="1" t="s">
-        <v>214</v>
+        <v>194</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>7</v>
+        <v>195</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>7</v>
+        <v>196</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>7</v>
+        <v>197</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>7</v>
+        <v>198</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>7</v>
+        <v>199</v>
       </c>
     </row>
     <row r="66" spans="1:6">
       <c r="A66" s="1" t="s">
-        <v>215</v>
+        <v>200</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>216</v>
+        <v>201</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>7</v>
@@ -3445,19 +3300,19 @@
     </row>
     <row r="67" spans="1:6">
       <c r="A67" s="1" t="s">
-        <v>217</v>
+        <v>202</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>218</v>
+        <v>7</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>219</v>
+        <v>203</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>7</v>
+        <v>204</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>7</v>
@@ -3465,53 +3320,53 @@
     </row>
     <row r="68" spans="1:6">
       <c r="A68" s="1" t="s">
-        <v>220</v>
+        <v>205</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>221</v>
+        <v>206</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>223</v>
+        <v>208</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>224</v>
+        <v>209</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
     </row>
     <row r="69" spans="1:6">
       <c r="A69" s="1" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>227</v>
+        <v>212</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>228</v>
+        <v>213</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>7</v>
+        <v>214</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>7</v>
+        <v>215</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>7</v>
+        <v>216</v>
       </c>
     </row>
     <row r="70" spans="1:6">
       <c r="A70" s="1" t="s">
-        <v>229</v>
+        <v>217</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>231</v>
+        <v>7</v>
       </c>
       <c r="D70" s="1" t="s">
         <v>7</v>
@@ -3520,12 +3375,12 @@
         <v>7</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>232</v>
+        <v>7</v>
       </c>
     </row>
     <row r="71" spans="1:6">
       <c r="A71" s="1" t="s">
-        <v>233</v>
+        <v>219</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>7</v>
@@ -3534,7 +3389,7 @@
         <v>7</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>234</v>
+        <v>7</v>
       </c>
       <c r="E71" s="1" t="s">
         <v>7</v>
@@ -3545,33 +3400,33 @@
     </row>
     <row r="72" spans="1:6">
       <c r="A72" s="1" t="s">
-        <v>235</v>
+        <v>220</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>236</v>
+        <v>221</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>237</v>
+        <v>222</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>238</v>
+        <v>223</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>239</v>
+        <v>224</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>240</v>
+        <v>225</v>
       </c>
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="1" t="s">
-        <v>241</v>
+        <v>226</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>242</v>
+        <v>7</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>243</v>
+        <v>7</v>
       </c>
       <c r="D73" s="1" t="s">
         <v>7</v>
@@ -3580,12 +3435,12 @@
         <v>7</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>244</v>
+        <v>7</v>
       </c>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="1" t="s">
-        <v>245</v>
+        <v>227</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>7</v>
@@ -3605,73 +3460,73 @@
     </row>
     <row r="75" spans="1:6">
       <c r="A75" s="1" t="s">
-        <v>246</v>
+        <v>228</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>247</v>
+        <v>229</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>248</v>
+        <v>230</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>249</v>
+        <v>231</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>250</v>
+        <v>232</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>251</v>
+        <v>233</v>
       </c>
     </row>
     <row r="76" spans="1:6">
       <c r="A76" s="1" t="s">
-        <v>252</v>
+        <v>234</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>7</v>
+        <v>235</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>7</v>
+        <v>236</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>7</v>
+        <v>237</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>7</v>
+        <v>238</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>7</v>
+        <v>239</v>
       </c>
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="1" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>254</v>
+        <v>241</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>7</v>
+        <v>242</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>255</v>
+        <v>243</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>7</v>
+        <v>244</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>7</v>
+        <v>245</v>
       </c>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="1" t="s">
-        <v>256</v>
+        <v>246</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>257</v>
+        <v>7</v>
       </c>
       <c r="D78" s="1" t="s">
         <v>7</v>
@@ -3685,16 +3540,16 @@
     </row>
     <row r="79" spans="1:6">
       <c r="A79" s="1" t="s">
-        <v>258</v>
+        <v>247</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>7</v>
+        <v>248</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>7</v>
+        <v>249</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="E79" s="1" t="s">
         <v>7</v>
@@ -3705,36 +3560,36 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="1" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>261</v>
+        <v>7</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>262</v>
+        <v>252</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>263</v>
+        <v>253</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>264</v>
+        <v>254</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>265</v>
+        <v>7</v>
       </c>
     </row>
     <row r="81" spans="1:6">
       <c r="A81" s="1" t="s">
-        <v>266</v>
+        <v>255</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>7</v>
+        <v>256</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>7</v>
+        <v>257</v>
       </c>
       <c r="E81" s="1" t="s">
         <v>7</v>
@@ -3745,30 +3600,30 @@
     </row>
     <row r="82" spans="1:6">
       <c r="A82" s="1" t="s">
-        <v>267</v>
+        <v>258</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>268</v>
+        <v>259</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>7</v>
+        <v>260</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
     </row>
     <row r="83" spans="1:6">
       <c r="A83" s="1" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>273</v>
+        <v>7</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>7</v>
@@ -3785,19 +3640,19 @@
     </row>
     <row r="84" spans="1:6">
       <c r="A84" s="1" t="s">
-        <v>274</v>
+        <v>265</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>275</v>
+        <v>7</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>276</v>
+        <v>7</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>277</v>
+        <v>7</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>7</v>
@@ -3805,53 +3660,53 @@
     </row>
     <row r="85" spans="1:6">
       <c r="A85" s="1" t="s">
-        <v>278</v>
+        <v>266</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>7</v>
+        <v>268</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>7</v>
+        <v>269</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>7</v>
+        <v>270</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>7</v>
+        <v>271</v>
       </c>
     </row>
     <row r="86" spans="1:6">
       <c r="A86" s="1" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>7</v>
+        <v>274</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>7</v>
+        <v>275</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>7</v>
+        <v>276</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>7</v>
+        <v>277</v>
       </c>
     </row>
     <row r="87" spans="1:6">
       <c r="A87" s="1" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>284</v>
+        <v>7</v>
       </c>
       <c r="D87" s="1" t="s">
         <v>7</v>
@@ -3865,19 +3720,19 @@
     </row>
     <row r="88" spans="1:6">
       <c r="A88" s="1" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>7</v>
@@ -3885,16 +3740,16 @@
     </row>
     <row r="89" spans="1:6">
       <c r="A89" s="1" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>7</v>
+        <v>286</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>7</v>
+        <v>287</v>
       </c>
       <c r="E89" s="1" t="s">
         <v>7</v>
@@ -3905,7 +3760,7 @@
     </row>
     <row r="90" spans="1:6">
       <c r="A90" s="1" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>7</v>
@@ -3925,22 +3780,22 @@
     </row>
     <row r="91" spans="1:6">
       <c r="A91" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="D91" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="B91" s="1" t="s">
+      <c r="E91" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="C91" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D91" s="1" t="s">
+      <c r="F91" s="1" t="s">
         <v>294</v>
-      </c>
-      <c r="E91" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F91" s="1" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="92" spans="1:6">
@@ -4004,7 +3859,7 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>
 </file>